--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.36149285758937</v>
+        <v>8.996242589358273</v>
       </c>
       <c r="D2" t="n">
-        <v>51.01374099597739</v>
+        <v>8.289732911846325</v>
       </c>
       <c r="E2" t="n">
-        <v>18.68825935530871</v>
+        <v>3.036842145237665</v>
       </c>
       <c r="F2" t="n">
-        <v>18.40145326970771</v>
+        <v>2.990236156327503</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.06201564907424</v>
+        <v>1.960077542974564</v>
       </c>
       <c r="D3" t="n">
-        <v>11.95849307794604</v>
+        <v>1.943255125166232</v>
       </c>
       <c r="E3" t="n">
-        <v>18.68825935530871</v>
+        <v>3.036842145237665</v>
       </c>
       <c r="F3" t="n">
-        <v>18.40145326970771</v>
+        <v>2.990236156327503</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.26101058385554</v>
+        <v>2.642414219876526</v>
       </c>
       <c r="D4" t="n">
-        <v>15.94660602218647</v>
+        <v>2.591323478605301</v>
       </c>
       <c r="E4" t="n">
-        <v>18.68825935530871</v>
+        <v>3.036842145237665</v>
       </c>
       <c r="F4" t="n">
-        <v>18.40145326970771</v>
+        <v>2.990236156327503</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>53.47418815626071</v>
+        <v>8.689555575392365</v>
       </c>
       <c r="D5" t="n">
-        <v>53.21888067349317</v>
+        <v>8.64806810944264</v>
       </c>
       <c r="E5" t="n">
-        <v>18.68825935530871</v>
+        <v>3.036842145237665</v>
       </c>
       <c r="F5" t="n">
-        <v>18.40145326970771</v>
+        <v>2.990236156327503</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.86500068138743</v>
+        <v>8.753062610725458</v>
       </c>
       <c r="D6" t="n">
-        <v>55.62635872062511</v>
+        <v>9.03928329210158</v>
       </c>
       <c r="E6" t="n">
-        <v>18.68825935530871</v>
+        <v>3.036842145237665</v>
       </c>
       <c r="F6" t="n">
-        <v>18.40145326970771</v>
+        <v>2.990236156327503</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13.84268809392594</v>
+        <v>2.249436815262965</v>
       </c>
       <c r="D7" t="n">
-        <v>13.68354641944973</v>
+        <v>2.223576293160581</v>
       </c>
       <c r="E7" t="n">
-        <v>18.68825935530871</v>
+        <v>3.036842145237665</v>
       </c>
       <c r="F7" t="n">
-        <v>18.40145326970771</v>
+        <v>2.990236156327503</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.95443608430937</v>
+        <v>6.167595863700273</v>
       </c>
       <c r="D8" t="n">
-        <v>38.44554791061167</v>
+        <v>6.247401535474397</v>
       </c>
       <c r="E8" t="n">
-        <v>18.68825935530871</v>
+        <v>3.036842145237665</v>
       </c>
       <c r="F8" t="n">
-        <v>18.40145326970771</v>
+        <v>2.990236156327503</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
